--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.62694926795111</v>
+        <v>3.026879256042056</v>
       </c>
       <c r="D2" t="n">
-        <v>18.97894056605287</v>
+        <v>3.084077841983591</v>
       </c>
       <c r="E2" t="n">
-        <v>9.672829481652784</v>
+        <v>1.571834790768577</v>
       </c>
       <c r="F2" t="n">
-        <v>9.823063669191326</v>
+        <v>1.596247846243591</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.18131716745638</v>
+        <v>7.829464039711663</v>
       </c>
       <c r="D3" t="n">
-        <v>46.72194118236182</v>
+        <v>7.592315442133796</v>
       </c>
       <c r="E3" t="n">
-        <v>9.672829481652784</v>
+        <v>1.571834790768577</v>
       </c>
       <c r="F3" t="n">
-        <v>9.823063669191326</v>
+        <v>1.596247846243591</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.86314299030987</v>
+        <v>5.502760735925355</v>
       </c>
       <c r="D4" t="n">
-        <v>32.29470885644387</v>
+        <v>5.247890189172129</v>
       </c>
       <c r="E4" t="n">
-        <v>9.672829481652784</v>
+        <v>1.571834790768577</v>
       </c>
       <c r="F4" t="n">
-        <v>9.823063669191326</v>
+        <v>1.596247846243591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.79435712917583</v>
+        <v>5.979083033491072</v>
       </c>
       <c r="D5" t="n">
-        <v>35.35072933110822</v>
+        <v>5.744493516305086</v>
       </c>
       <c r="E5" t="n">
-        <v>9.672829481652784</v>
+        <v>1.571834790768577</v>
       </c>
       <c r="F5" t="n">
-        <v>9.823063669191326</v>
+        <v>1.596247846243591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.54633223928465</v>
+        <v>5.613778988883756</v>
       </c>
       <c r="D6" t="n">
-        <v>34.75302718240783</v>
+        <v>5.647366917141273</v>
       </c>
       <c r="E6" t="n">
-        <v>9.672829481652784</v>
+        <v>1.571834790768577</v>
       </c>
       <c r="F6" t="n">
-        <v>9.823063669191326</v>
+        <v>1.596247846243591</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.57235280406345</v>
+        <v>3.66800733066031</v>
       </c>
       <c r="D7" t="n">
-        <v>18.64395180146929</v>
+        <v>3.02964216773876</v>
       </c>
       <c r="E7" t="n">
-        <v>9.672829481652784</v>
+        <v>1.571834790768577</v>
       </c>
       <c r="F7" t="n">
-        <v>9.823063669191326</v>
+        <v>1.596247846243591</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
